--- a/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
+++ b/apps/excel-service/templates/XANSHA/HOTEL/Tax Invoice.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Условия оплаты по договору (контракту): наличный расчет</t>
   </si>
   <si>
-    <t xml:space="preserve">Пункт назначения поставляемых товаров (работ, услуг): Республика Казахстан,  Улытауская область, п.Жанаарка,Жанааркинскии район, улица Сарыарка № 6</t>
+    <t xml:space="preserve">Пункт назначения поставляемых товаров (работ, услуг): Республика Казахстан,  Улытауская область, п.Жанаарка,Жанааркинскии район, улица {documentAddress}</t>
   </si>
   <si>
     <t xml:space="preserve">государство, регион, область, город, район</t>
